--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567649</v>
+        <v>122567519</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577631</v>
+        <v>577659</v>
       </c>
       <c r="R2" t="n">
-        <v>7047709</v>
+        <v>7047666</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567426</v>
+        <v>122567415</v>
       </c>
       <c r="B3" t="n">
-        <v>90844</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,31 +813,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577666</v>
+        <v>577665</v>
       </c>
       <c r="R3" t="n">
-        <v>7047652</v>
+        <v>7047625</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567519</v>
+        <v>122567426</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,27 +935,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577659</v>
+        <v>577666</v>
       </c>
       <c r="R4" t="n">
-        <v>7047666</v>
+        <v>7047652</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567250</v>
+        <v>122567286</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,39 +1056,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577683</v>
+        <v>577696</v>
       </c>
       <c r="R5" t="n">
-        <v>7047626</v>
+        <v>7047629</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,12 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,19 +1140,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567415</v>
+        <v>122567504</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1198,7 +1188,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1207,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577665</v>
+        <v>577648</v>
       </c>
       <c r="R6" t="n">
-        <v>7047625</v>
+        <v>7047682</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,12 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567286</v>
+        <v>122567250</v>
       </c>
       <c r="B7" t="n">
-        <v>90826</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,34 +1290,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577696</v>
+        <v>577683</v>
       </c>
       <c r="R7" t="n">
-        <v>7047629</v>
+        <v>7047626</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1364,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,19 +1384,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567504</v>
+        <v>122567649</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577648</v>
+        <v>577631</v>
       </c>
       <c r="R8" t="n">
-        <v>7047682</v>
+        <v>7047709</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567519</v>
+        <v>122567426</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577659</v>
+        <v>577666</v>
       </c>
       <c r="R2" t="n">
-        <v>7047666</v>
+        <v>7047652</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567415</v>
+        <v>122567286</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>90839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577665</v>
+        <v>577696</v>
       </c>
       <c r="R3" t="n">
-        <v>7047625</v>
+        <v>7047629</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567426</v>
+        <v>122567649</v>
       </c>
       <c r="B4" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +924,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -968,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577666</v>
+        <v>577631</v>
       </c>
       <c r="R4" t="n">
-        <v>7047652</v>
+        <v>7047709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,22 +1018,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567286</v>
+        <v>122567250</v>
       </c>
       <c r="B5" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,34 +1046,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577696</v>
+        <v>577683</v>
       </c>
       <c r="R5" t="n">
-        <v>7047629</v>
+        <v>7047626</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,12 +1140,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567250</v>
+        <v>122567519</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1310,7 +1310,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577683</v>
+        <v>577659</v>
       </c>
       <c r="R7" t="n">
-        <v>7047626</v>
+        <v>7047666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1396,7 +1396,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567649</v>
+        <v>122567415</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1432,7 +1432,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577631</v>
+        <v>577665</v>
       </c>
       <c r="R8" t="n">
-        <v>7047709</v>
+        <v>7047625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567426</v>
+        <v>122567649</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577666</v>
+        <v>577631</v>
       </c>
       <c r="R2" t="n">
-        <v>7047652</v>
+        <v>7047709</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567286</v>
+        <v>122567250</v>
       </c>
       <c r="B3" t="n">
-        <v>90839</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577696</v>
+        <v>577683</v>
       </c>
       <c r="R3" t="n">
-        <v>7047629</v>
+        <v>7047626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567649</v>
+        <v>122567286</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>90833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577631</v>
+        <v>577696</v>
       </c>
       <c r="R4" t="n">
-        <v>7047709</v>
+        <v>7047629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567250</v>
+        <v>122567504</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1066,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577683</v>
+        <v>577648</v>
       </c>
       <c r="R5" t="n">
-        <v>7047626</v>
+        <v>7047682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1140,19 +1141,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567504</v>
+        <v>122567415</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1188,7 +1189,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1197,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577648</v>
+        <v>577665</v>
       </c>
       <c r="R6" t="n">
-        <v>7047682</v>
+        <v>7047625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567519</v>
+        <v>122567426</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,27 +1291,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1319,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577659</v>
+        <v>577666</v>
       </c>
       <c r="R7" t="n">
-        <v>7047666</v>
+        <v>7047652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,12 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,7 +1396,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567415</v>
+        <v>122567519</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1432,7 +1432,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577665</v>
+        <v>577659</v>
       </c>
       <c r="R8" t="n">
-        <v>7047625</v>
+        <v>7047666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,12 +1506,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567649</v>
+        <v>122567286</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>90833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577631</v>
+        <v>577696</v>
       </c>
       <c r="R2" t="n">
-        <v>7047709</v>
+        <v>7047629</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567250</v>
+        <v>122567504</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -833,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577683</v>
+        <v>577648</v>
       </c>
       <c r="R3" t="n">
-        <v>7047626</v>
+        <v>7047682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567286</v>
+        <v>122567519</v>
       </c>
       <c r="B4" t="n">
-        <v>90833</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577696</v>
+        <v>577659</v>
       </c>
       <c r="R4" t="n">
-        <v>7047629</v>
+        <v>7047666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,19 +1019,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567504</v>
+        <v>122567415</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1067,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577648</v>
+        <v>577665</v>
       </c>
       <c r="R5" t="n">
-        <v>7047682</v>
+        <v>7047625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567415</v>
+        <v>122567250</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577665</v>
+        <v>577683</v>
       </c>
       <c r="R6" t="n">
-        <v>7047625</v>
+        <v>7047626</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,12 +1263,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1396,7 +1396,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567519</v>
+        <v>122567649</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577659</v>
+        <v>577631</v>
       </c>
       <c r="R8" t="n">
-        <v>7047666</v>
+        <v>7047709</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1506,12 +1506,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567286</v>
+        <v>122567519</v>
       </c>
       <c r="B2" t="n">
-        <v>90833</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577696</v>
+        <v>577659</v>
       </c>
       <c r="R2" t="n">
-        <v>7047629</v>
+        <v>7047666</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567504</v>
+        <v>122567286</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>90834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577648</v>
+        <v>577696</v>
       </c>
       <c r="R3" t="n">
-        <v>7047682</v>
+        <v>7047629</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567519</v>
+        <v>122567504</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577659</v>
+        <v>577648</v>
       </c>
       <c r="R4" t="n">
-        <v>7047666</v>
+        <v>7047682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1019,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567415</v>
+        <v>122567649</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577665</v>
+        <v>577631</v>
       </c>
       <c r="R5" t="n">
-        <v>7047625</v>
+        <v>7047709</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567250</v>
+        <v>122567426</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>90852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,27 +1169,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1198,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577683</v>
+        <v>577666</v>
       </c>
       <c r="R6" t="n">
-        <v>7047626</v>
+        <v>7047652</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567426</v>
+        <v>122567250</v>
       </c>
       <c r="B7" t="n">
-        <v>90851</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,31 +1290,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1324,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577666</v>
+        <v>577683</v>
       </c>
       <c r="R7" t="n">
-        <v>7047652</v>
+        <v>7047626</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1364,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567649</v>
+        <v>122567415</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577631</v>
+        <v>577665</v>
       </c>
       <c r="R8" t="n">
-        <v>7047709</v>
+        <v>7047625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567519</v>
+        <v>122567649</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577659</v>
+        <v>577631</v>
       </c>
       <c r="R2" t="n">
-        <v>7047666</v>
+        <v>7047709</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567286</v>
+        <v>122567250</v>
       </c>
       <c r="B3" t="n">
-        <v>90834</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577696</v>
+        <v>577683</v>
       </c>
       <c r="R3" t="n">
-        <v>7047629</v>
+        <v>7047626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,19 +907,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567504</v>
+        <v>122567415</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -945,7 +955,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577648</v>
+        <v>577665</v>
       </c>
       <c r="R4" t="n">
-        <v>7047682</v>
+        <v>7047625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567649</v>
+        <v>122567504</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1076,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577631</v>
+        <v>577648</v>
       </c>
       <c r="R5" t="n">
-        <v>7047709</v>
+        <v>7047682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1153,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567426</v>
+        <v>122567519</v>
       </c>
       <c r="B6" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,31 +1179,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1202,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577666</v>
+        <v>577659</v>
       </c>
       <c r="R6" t="n">
-        <v>7047652</v>
+        <v>7047666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567250</v>
+        <v>122567426</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,27 +1301,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1319,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577683</v>
+        <v>577666</v>
       </c>
       <c r="R7" t="n">
-        <v>7047626</v>
+        <v>7047652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,12 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567415</v>
+        <v>122567286</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>90837</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,39 +1422,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577665</v>
+        <v>577696</v>
       </c>
       <c r="R8" t="n">
-        <v>7047625</v>
+        <v>7047629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567649</v>
+        <v>122567426</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577631</v>
+        <v>577666</v>
       </c>
       <c r="R2" t="n">
-        <v>7047709</v>
+        <v>7047652</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,19 +784,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567250</v>
+        <v>122567504</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -833,7 +832,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577683</v>
+        <v>577648</v>
       </c>
       <c r="R3" t="n">
-        <v>7047626</v>
+        <v>7047682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,22 +906,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567415</v>
+        <v>122567286</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>90837</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,39 +934,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577665</v>
+        <v>577696</v>
       </c>
       <c r="R4" t="n">
-        <v>7047625</v>
+        <v>7047629</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567504</v>
+        <v>122567649</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1086,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577648</v>
+        <v>577631</v>
       </c>
       <c r="R5" t="n">
-        <v>7047682</v>
+        <v>7047709</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1163,7 +1152,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567519</v>
+        <v>122567250</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1199,7 +1188,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577659</v>
+        <v>577683</v>
       </c>
       <c r="R6" t="n">
-        <v>7047666</v>
+        <v>7047626</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1285,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567426</v>
+        <v>122567519</v>
       </c>
       <c r="B7" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,31 +1290,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1334,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577666</v>
+        <v>577659</v>
       </c>
       <c r="R7" t="n">
-        <v>7047652</v>
+        <v>7047666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1364,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567286</v>
+        <v>122567415</v>
       </c>
       <c r="B8" t="n">
-        <v>90837</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,34 +1412,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577696</v>
+        <v>577665</v>
       </c>
       <c r="R8" t="n">
-        <v>7047629</v>
+        <v>7047625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567519</v>
+        <v>122567250</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577659</v>
+        <v>577683</v>
       </c>
       <c r="R2" t="n">
-        <v>7047666</v>
+        <v>7047626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567504</v>
+        <v>122567649</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577648</v>
+        <v>577631</v>
       </c>
       <c r="R3" t="n">
-        <v>7047682</v>
+        <v>7047709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567286</v>
+        <v>122567415</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +935,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577696</v>
+        <v>577665</v>
       </c>
       <c r="R4" t="n">
-        <v>7047629</v>
+        <v>7047625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567415</v>
+        <v>122567519</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1067,7 +1077,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577665</v>
+        <v>577659</v>
       </c>
       <c r="R5" t="n">
-        <v>7047625</v>
+        <v>7047666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,22 +1151,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567426</v>
+        <v>122567504</v>
       </c>
       <c r="B6" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,31 +1179,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1202,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577666</v>
+        <v>577648</v>
       </c>
       <c r="R6" t="n">
-        <v>7047652</v>
+        <v>7047682</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,22 +1273,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567649</v>
+        <v>122567426</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,27 +1301,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1319,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577631</v>
+        <v>577666</v>
       </c>
       <c r="R7" t="n">
-        <v>7047709</v>
+        <v>7047652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,12 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,22 +1394,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567250</v>
+        <v>122567286</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,39 +1422,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577683</v>
+        <v>577696</v>
       </c>
       <c r="R8" t="n">
-        <v>7047626</v>
+        <v>7047629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,12 +1506,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567250</v>
+        <v>122567649</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577683</v>
+        <v>577631</v>
       </c>
       <c r="R2" t="n">
-        <v>7047626</v>
+        <v>7047709</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,19 +785,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567649</v>
+        <v>122567250</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -833,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577631</v>
+        <v>577683</v>
       </c>
       <c r="R3" t="n">
-        <v>7047709</v>
+        <v>7047626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -907,19 +907,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567415</v>
+        <v>122567519</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -955,7 +955,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577665</v>
+        <v>577659</v>
       </c>
       <c r="R4" t="n">
-        <v>7047625</v>
+        <v>7047666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,22 +1029,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567519</v>
+        <v>122567426</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,27 +1057,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577659</v>
+        <v>577666</v>
       </c>
       <c r="R5" t="n">
-        <v>7047666</v>
+        <v>7047652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567504</v>
+        <v>122567286</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,39 +1178,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577648</v>
+        <v>577696</v>
       </c>
       <c r="R6" t="n">
-        <v>7047682</v>
+        <v>7047629</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567426</v>
+        <v>122567415</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,31 +1290,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1334,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577666</v>
+        <v>577665</v>
       </c>
       <c r="R7" t="n">
-        <v>7047652</v>
+        <v>7047625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1364,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,22 +1384,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567286</v>
+        <v>122567504</v>
       </c>
       <c r="B8" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,34 +1412,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577696</v>
+        <v>577648</v>
       </c>
       <c r="R8" t="n">
-        <v>7047629</v>
+        <v>7047682</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567649</v>
+        <v>122567415</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577631</v>
+        <v>577665</v>
       </c>
       <c r="R2" t="n">
-        <v>7047709</v>
+        <v>7047625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567250</v>
+        <v>122567519</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -833,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577683</v>
+        <v>577659</v>
       </c>
       <c r="R3" t="n">
-        <v>7047626</v>
+        <v>7047666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567519</v>
+        <v>122567250</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -955,7 +955,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577659</v>
+        <v>577683</v>
       </c>
       <c r="R4" t="n">
-        <v>7047666</v>
+        <v>7047626</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567426</v>
+        <v>122567649</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,31 +1057,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1090,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577666</v>
+        <v>577631</v>
       </c>
       <c r="R5" t="n">
-        <v>7047652</v>
+        <v>7047709</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,12 +1151,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1274,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567415</v>
+        <v>122567426</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,27 +1291,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1319,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577665</v>
+        <v>577666</v>
       </c>
       <c r="R7" t="n">
-        <v>7047625</v>
+        <v>7047652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,12 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,12 +1384,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122567415</v>
+        <v>122567286</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577665</v>
+        <v>577696</v>
       </c>
       <c r="R2" t="n">
-        <v>7047625</v>
+        <v>7047629</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567519</v>
+        <v>122567250</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -833,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577659</v>
+        <v>577683</v>
       </c>
       <c r="R3" t="n">
-        <v>7047666</v>
+        <v>7047626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567250</v>
+        <v>122567649</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -955,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577683</v>
+        <v>577631</v>
       </c>
       <c r="R4" t="n">
-        <v>7047626</v>
+        <v>7047709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,19 +1019,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567649</v>
+        <v>122567519</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1086,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577631</v>
+        <v>577659</v>
       </c>
       <c r="R5" t="n">
-        <v>7047709</v>
+        <v>7047666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1151,22 +1141,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122567286</v>
+        <v>122567504</v>
       </c>
       <c r="B6" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,34 +1169,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577696</v>
+        <v>577648</v>
       </c>
       <c r="R6" t="n">
-        <v>7047629</v>
+        <v>7047682</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1396,7 +1396,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567504</v>
+        <v>122567415</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1432,7 +1432,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577648</v>
+        <v>577665</v>
       </c>
       <c r="R8" t="n">
-        <v>7047682</v>
+        <v>7047625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>122567286</v>
       </c>
       <c r="B2" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122567250</v>
+        <v>122566768</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577683</v>
+        <v>577712</v>
       </c>
       <c r="R3" t="n">
-        <v>7047626</v>
+        <v>7047643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122567649</v>
+        <v>122567250</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,7 +930,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577631</v>
+        <v>577683</v>
       </c>
       <c r="R4" t="n">
-        <v>7047709</v>
+        <v>7047626</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1019,27 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122567519</v>
+        <v>122567415</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577659</v>
+        <v>577665</v>
       </c>
       <c r="R5" t="n">
-        <v>7047666</v>
+        <v>7047625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,12 +1121,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1156,12 +1136,7 @@
         <v>122567504</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,15 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122567426</v>
+        <v>122567519</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,31 +1261,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1324,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577666</v>
+        <v>577659</v>
       </c>
       <c r="R7" t="n">
-        <v>7047652</v>
+        <v>7047666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,15 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122567415</v>
+        <v>122567600</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1398,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1441,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577665</v>
+        <v>577658</v>
       </c>
       <c r="R8" t="n">
-        <v>7047625</v>
+        <v>7047696</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1452,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,15 +1472,366 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122567603</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kallrå, Kallrå, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577640</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7047712</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122567649</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kallrå, Kallrå, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577631</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7047709</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122567856</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kallrå, Kallrå, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577598</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7047750</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5121-2025 artfynd.xlsx
+++ b/artfynd/A 5121-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567286</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566768</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567250</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567415</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567504</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567519</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567600</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567603</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1715,6 +1760,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567649</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,8 +1882,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122567856</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>